--- a/results/Supplementary_Table_8_Hits_intersections.xlsx
+++ b/results/Supplementary_Table_8_Hits_intersections.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,32 +429,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>HOG</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Sets</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>U. diversus gene ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>U. diversus GO terms</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>U. diversus gene description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>P. tepidariorum best BLAST hit for the HOG</t>
         </is>
@@ -2897,12 +2909,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>129226559</t>
+          <t>129226969</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>GO:0061630 [Name: ubiquitin protein ligase activity]; GO:0005634 [Name: nucleus]; GO:0005515 [Name: protein binding]; GO:0051092 [Name: positive regulation of NF-kappaB transcription factor activity]; GO:0016567 [Name: protein ubiquitination]</t>
+          <t>GO:0051092 [Name: positive regulation of NF-kappaB transcription factor activity]; GO:0016567 [Name: protein ubiquitination]; GO:0061630 [Name: ubiquitin protein ligase activity]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4731,9 +4743,21 @@
           <t>intensified_in_nonorb, positive_sel_in_nonorb</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>129218569</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>uncharacterized LOC129218569</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
           <t>uncharacterized protein isoform X1</t>
@@ -5111,9 +5135,21 @@
           <t>duplication_more_likely_orb, loss_more_likely_nonorb</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>129221006</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>GO:0006511 [Name: ubiquitin-dependent protein catabolic process]; GO:0061630 [Name: ubiquitin protein ligase activity]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>E3 ubiquitin-protein ligase RLIM-like</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
@@ -6539,21 +6575,9 @@
           <t>silk_genes, spidroins</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>129227027</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>serine-rich adhesin for platelets-like</t>
-        </is>
-      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -6569,7 +6593,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>129224650</t>
+          <t>129223990</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -6765,17 +6789,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>129231571</t>
+          <t>129223990</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>GO:0016627 [Name: oxidoreductase activity, acting on the CH-CH group of donors]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>acyl-CoA dehydrogenase family member 11-like</t>
+          <t>fibroin heavy chain-like</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -8829,7 +8853,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>129233808</t>
+          <t>129229510</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -8839,7 +8863,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>bis(5'-nucleosyl)-tetraphosphatase PrpE [asymmetrical]-like</t>
+          <t>bis(5'-nucleosyl)-tetraphosphatase, symmetrical-like</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -11255,21 +11279,9 @@
           <t>silk_genes, phyloglm_fg</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>129229398</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>GO:0005764 [Name: lysosome]; GO:0051603 [Name: proteolysis involved in cellular protein catabolic process]; GO:0004197 [Name: cysteine-type endopeptidase activity]; GO:0005615 [Name: extracellular space]</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>procathepsin L-like</t>
-        </is>
-      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
           <t>cathepsin L-like peptidase</t>
@@ -11309,7 +11321,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>129231241</t>
+          <t>129231419</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -11319,7 +11331,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>putative methyltransferase-like protein 7A</t>
+          <t>thiol S-methyltransferase METTL7B-like</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -12561,17 +12573,17 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>129216775</t>
+          <t>129229580</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>GO:0019185 [Name: snRNA-activating protein complex]; GO:0042795 [Name: snRNA transcription from RNA polymerase II promoter]; GO:0042796 [Name: snRNA transcription from RNA polymerase III promoter]; GO:0043565 [Name: sequence-specific DNA binding]</t>
+          <t>GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129216775</t>
+          <t>Krueppel-like factor 13</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
